--- a/Amefa Order Portal/amefa_order_portal_demo_db_final_en.xlsx
+++ b/Amefa Order Portal/amefa_order_portal_demo_db_final_en.xlsx
@@ -31961,7 +31961,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F2"/>
+  <dimension ref="A1:F3"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="16.28515625" defaultRowHeight="15"/>
   <sheetData>
     <row r="1" ht="20.1" customHeight="1">
@@ -32023,6 +32023,38 @@
         </is>
       </c>
       <c r="F2" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>AME-000004</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>CUST-008</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>A-10346</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>AME-000004</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>2026-01-28 14:02:39</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
         <is>
           <t>Open</t>
         </is>

--- a/Amefa Order Portal/amefa_order_portal_demo_db_final_en.xlsx
+++ b/Amefa Order Portal/amefa_order_portal_demo_db_final_en.xlsx
@@ -699,7 +699,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E55"/>
+  <dimension ref="A1:E56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16.7109375" customWidth="1" min="1" max="1"/>
@@ -2190,6 +2190,33 @@
       <c r="E55" t="inlineStr">
         <is>
           <t>2026-02-01 20:23:27</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>C0002</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>Roland</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>roland@gmail.com</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>test12345</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>2026-02-01 20:42:11</t>
         </is>
       </c>
     </row>
